--- a/data/trans_camb/P8_1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P8_1_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,9</t>
+          <t>1,08; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,69</t>
+          <t>1,58; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,46</t>
+          <t>2,08; 9,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,32</t>
+          <t>2,02; 10,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,49</t>
+          <t>1,27; 10,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,26</t>
+          <t>-4,64; 4,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,69</t>
+          <t>2,54; 8,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,29</t>
+          <t>2,35; 8,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,31</t>
+          <t>0,23; 6,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,64; 85,43</t>
+          <t>7,99; 88,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 95,37</t>
+          <t>12,8; 92,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,25; 105,97</t>
+          <t>14,95; 101,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 59,93</t>
+          <t>9,21; 59,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 55,84</t>
+          <t>5,57; 56,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 22,79</t>
+          <t>-19,94; 22,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 60,75</t>
+          <t>15,31; 61,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,53; 58,16</t>
+          <t>14,08; 59,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 45,33</t>
+          <t>1,41; 43,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,62</t>
+          <t>1,55; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,43</t>
+          <t>0,45; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 50,9</t>
+          <t>-0,7; 53,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,99</t>
+          <t>-0,57; 6,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,81</t>
+          <t>-1,65; 5,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,51</t>
+          <t>-2,96; 3,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,53</t>
+          <t>1,49; 6,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,41</t>
+          <t>0,33; 5,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 33,61</t>
+          <t>-0,41; 34,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 77,95</t>
+          <t>11,55; 76,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 66,61</t>
+          <t>3,55; 65,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 515,13</t>
+          <t>-6,76; 559,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 36,45</t>
+          <t>-2,44; 34,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 30,01</t>
+          <t>-7,17; 30,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 18,57</t>
+          <t>-12,76; 20,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 43,46</t>
+          <t>8,15; 43,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 36,35</t>
+          <t>1,96; 36,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 216,1</t>
+          <t>-2,43; 221,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,61</t>
+          <t>-3,45; 3,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 4,16</t>
+          <t>-2,75; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,53</t>
+          <t>1,45; 9,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,52</t>
+          <t>-5,53; 3,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 0,67</t>
+          <t>-7,69; 1,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -2,6</t>
+          <t>-18,73; -2,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,48</t>
+          <t>-3,05; 2,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,31</t>
+          <t>-4,26; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,73</t>
+          <t>-7,37; 2,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 34,3</t>
+          <t>-25,77; 37,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 41,7</t>
+          <t>-20,01; 42,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,71; 93,32</t>
+          <t>9,78; 91,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 15,79</t>
+          <t>-20,56; 17,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 2,57</t>
+          <t>-28,9; 4,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,23; -11,02</t>
+          <t>-69,0; -10,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 14,81</t>
+          <t>-15,79; 16,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 8,14</t>
+          <t>-21,41; 7,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 9,44</t>
+          <t>-39,02; 11,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,03</t>
+          <t>0,95; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,72</t>
+          <t>-1,17; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,73</t>
+          <t>1,16; 7,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,85</t>
+          <t>2,76; 9,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,97</t>
+          <t>-3,37; 4,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,99</t>
+          <t>-3,05; 6,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,53</t>
+          <t>2,41; 7,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,57</t>
+          <t>-1,39; 3,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,73</t>
+          <t>0,58; 5,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 72,34</t>
+          <t>7,98; 74,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 51,08</t>
+          <t>-9,72; 48,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 71,68</t>
+          <t>9,46; 72,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 53,63</t>
+          <t>12,45; 52,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 21,76</t>
+          <t>-15,73; 21,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 32,55</t>
+          <t>-13,72; 34,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,95; 51,8</t>
+          <t>14,09; 51,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 24,91</t>
+          <t>-8,08; 24,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 39,55</t>
+          <t>3,56; 39,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,17</t>
+          <t>1,83; 5,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,21</t>
+          <t>1,14; 4,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 27,54</t>
+          <t>3,12; 27,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,93</t>
+          <t>1,86; 5,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,13</t>
+          <t>-0,6; 3,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,23</t>
+          <t>-5,18; 1,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,09</t>
+          <t>2,5; 5,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,35</t>
+          <t>0,56; 3,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 14,55</t>
+          <t>0,72; 13,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>15,04; 49,25</t>
+          <t>15,63; 50,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,69; 40,97</t>
+          <t>9,72; 40,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25,68; 257,17</t>
+          <t>27,24; 254,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,08; 29,41</t>
+          <t>8,41; 28,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 15,36</t>
+          <t>-2,68; 16,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 5,78</t>
+          <t>-23,32; 5,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,25; 32,01</t>
+          <t>14,81; 31,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,56; 21,05</t>
+          <t>3,29; 20,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,72; 86,65</t>
+          <t>4,42; 82,99</t>
         </is>
       </c>
     </row>
